--- a/imorexport/employee_settings.xlsx
+++ b/imorexport/employee_settings.xlsx
@@ -1,25 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T02363\Downloads\shiftsceduler\imorexport\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T02363\Documents\shiftsceduler\imorexport\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A32C314-F85D-4E7D-AE1C-9AD5B4024E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10935"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="employee_settings" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="71">
   <si>
     <t>emp_id</t>
   </si>
@@ -99,12 +105,6 @@
     <t>NIGHT_ONLY</t>
   </si>
   <si>
-    <t>T02504</t>
-  </si>
-  <si>
-    <t>潘元浩</t>
-  </si>
-  <si>
     <t>T02505</t>
   </si>
   <si>
@@ -277,30 +277,6 @@
   </si>
   <si>
     <t>簡悅如</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>ny</t>
-    </r>
-  </si>
-  <si>
-    <t>T02498</t>
-  </si>
-  <si>
-    <t>張芯瑜</t>
   </si>
   <si>
     <r>
@@ -448,7 +424,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -726,8 +702,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G1000"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G998"/>
   <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="5.25" customWidth="1"/>
@@ -754,7 +730,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -800,7 +776,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -822,8 +798,8 @@
       <c r="F4" s="1">
         <v>1</v>
       </c>
-      <c r="G4" s="2">
-        <v>3</v>
+      <c r="G4" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -846,7 +822,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -869,7 +845,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -892,7 +868,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -908,14 +884,14 @@
       <c r="D8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="1">
-        <v>6</v>
+      <c r="E8" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="F8" s="1">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -935,10 +911,10 @@
         <v>14</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -952,7 +928,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>14</v>
@@ -961,21 +937,21 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>14</v>
@@ -984,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -995,10 +971,10 @@
         <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>14</v>
@@ -1006,134 +982,134 @@
       <c r="F12" s="1">
         <v>1</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>38</v>
+      <c r="G12" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="D13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="1">
         <v>1</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="1">
         <v>1</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>14</v>
+      <c r="E15" s="1">
+        <v>5</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E16" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" s="1">
         <v>1</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="1">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="F17" s="1">
         <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>9</v>
@@ -1145,21 +1121,21 @@
         <v>1</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>14</v>
@@ -1168,44 +1144,44 @@
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>14</v>
@@ -1214,21 +1190,21 @@
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>14</v>
@@ -1237,21 +1213,21 @@
         <v>1</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>14</v>
@@ -1260,55 +1236,11 @@
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="1">
-        <v>1</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
+    <row r="24" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1507,8 +1439,8 @@
     <row r="221" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="222" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="223" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2282,8 +2214,6 @@
     <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
